--- a/data/batches/B02_DM_arm_age_flags/Test_Validation_Report/Test_Validation_Report_B02.xlsx
+++ b/data/batches/B02_DM_arm_age_flags/Test_Validation_Report/Test_Validation_Report_B02.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -6787,11 +6787,7 @@
           <t>INCONSISTENT ARM</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>INCONSISTENT ARM</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6799,22 +6795,22 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6866,11 +6862,7 @@
           <t>INCONSISTENT ARM</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>INCONSISTENT ARM</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6878,22 +6870,22 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -6945,11 +6937,7 @@
           <t>INCONSISTENT ARM</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>INCONSISTENT ARM</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6957,22 +6945,22 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7024,11 +7012,7 @@
           <t>INCONSISTENT ARM</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>INCONSISTENT ARM</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7036,22 +7020,22 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7103,11 +7087,7 @@
           <t>INCONSISTENT ARM</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>INCONSISTENT ARM</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7115,22 +7095,22 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7182,11 +7162,7 @@
           <t>INCONSISTENT_CD</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>INCONSISTENT_CD</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7194,22 +7170,22 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7336,11 +7312,7 @@
           <t>INCONSISTENT_CD</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>INCONSISTENT_CD</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7348,22 +7320,22 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7415,11 +7387,7 @@
           <t>INCONSISTENT_CD</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>INCONSISTENT_CD</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7427,22 +7395,22 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -7494,11 +7462,7 @@
           <t>INCONSISTENT_CD</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>INCONSISTENT_CD</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -7506,22 +7470,22 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8728,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -8815,7 +8779,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -10895,10 +10859,10 @@
         <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -10913,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>62.07</v>
+        <v>58.62</v>
       </c>
     </row>
   </sheetData>
